--- a/data/trans_orig/IP24_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP24_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el ejercicio físico  que realiza en su tiempo libre / solo 2023 en 2023 (tasa de respuesta: 99,43%)</t>
+          <t>Menores según el ejercicio físico que realiza en su tiempo libre / solo 2023 en 2023 (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>860</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>722</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13630</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13937</t>
+          <t>12745</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12750</t>
+          <t>12224</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22000</t>
+          <t>22090</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18262</t>
+          <t>17262</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35143</t>
+          <t>34930</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26729</t>
+          <t>26506</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40449</t>
+          <t>41020</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48368</t>
+          <t>49002</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71344</t>
+          <t>71314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,61%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27162</t>
+          <t>28677</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6689</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17609</t>
+          <t>17748</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16809</t>
+          <t>16520</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41650</t>
+          <t>41636</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,97%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>482</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>784</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2351</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7589</t>
+          <t>7557</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19211</t>
+          <t>19197</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13910</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14400</t>
+          <t>14302</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28618</t>
+          <t>28394</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24309</t>
+          <t>24161</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46839</t>
+          <t>46006</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43789</t>
+          <t>45015</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70806</t>
+          <t>71541</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>73289</t>
+          <t>73775</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>109289</t>
+          <t>110101</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62456</t>
+          <t>62328</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94667</t>
+          <t>94773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>111569</t>
+          <t>109368</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>151572</t>
+          <t>152368</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>179655</t>
+          <t>181754</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>237309</t>
+          <t>236416</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>180144</t>
+          <t>182112</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>242183</t>
+          <t>244163</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>204055</t>
+          <t>200730</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>251060</t>
+          <t>250668</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>399574</t>
+          <t>404786</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>479101</t>
+          <t>482251</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,6%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67518</t>
+          <t>67650</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>163267</t>
+          <t>170230</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>56763</t>
+          <t>55737</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>104216</t>
+          <t>105430</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>132699</t>
+          <t>132668</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>240888</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12595</t>
+          <t>12651</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26463</t>
+          <t>26694</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13042</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28714</t>
+          <t>28686</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28373</t>
+          <t>28768</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48366</t>
+          <t>48199</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>915</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6956</t>
+          <t>7073</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>9931</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12853</t>
+          <t>13424</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27427</t>
+          <t>26586</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27456</t>
+          <t>27107</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47166</t>
+          <t>46349</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45252</t>
+          <t>44608</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67060</t>
+          <t>67742</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31228</t>
+          <t>30604</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49531</t>
+          <t>48357</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37051</t>
+          <t>36700</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60867</t>
+          <t>61199</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>73448</t>
+          <t>73585</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>103427</t>
+          <t>103055</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,03%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52729</t>
+          <t>53486</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>72951</t>
+          <t>73335</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>54382</t>
+          <t>54681</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>78038</t>
+          <t>78808</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>114775</t>
+          <t>114379</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>144631</t>
+          <t>145099</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,69%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14664</t>
+          <t>14984</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29187</t>
+          <t>29720</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16286</t>
+          <t>16562</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33986</t>
+          <t>33123</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34424</t>
+          <t>35140</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55715</t>
+          <t>55622</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8557</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>10940</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15890</t>
+          <t>15816</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>9962</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22134</t>
+          <t>21940</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8989</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20840</t>
+          <t>19949</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20534</t>
+          <t>20455</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36982</t>
+          <t>36333</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43974</t>
+          <t>45001</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>69556</t>
+          <t>71429</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>79863</t>
+          <t>81121</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>118002</t>
+          <t>114773</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>131974</t>
+          <t>130717</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>175595</t>
+          <t>173814</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>104257</t>
+          <t>105792</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>143290</t>
+          <t>145147</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>160068</t>
+          <t>164197</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>208894</t>
+          <t>211456</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>278987</t>
+          <t>275879</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>340051</t>
+          <t>340590</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>266342</t>
+          <t>270023</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>337554</t>
+          <t>338815</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>300735</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>354319</t>
+          <t>354232</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>591215</t>
+          <t>588080</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>677192</t>
+          <t>676870</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,66%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>100312</t>
+          <t>99267</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>215518</t>
+          <t>206647</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>90871</t>
+          <t>89522</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>142995</t>
+          <t>140398</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>199902</t>
+          <t>200870</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>325991</t>
+          <t>318556</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17642</t>
+          <t>17978</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33938</t>
+          <t>33905</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19440</t>
+          <t>20456</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>37067</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>41770</t>
+          <t>41479</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>66202</t>
+          <t>65192</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP24_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP24_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2153</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,34%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2198</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2388</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>860</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5749</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2818</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>815</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7246</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>10190</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>779</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12597</t>
+          <t>14319</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6264</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2937</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10890</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11,23%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,27%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>19,53%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7436</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3200</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12745</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,6%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>23,31%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6849</t>
+          <t>8619</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12224</t>
+          <t>15506</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>14284</t>
+          <t>14883</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22090</t>
+          <t>23324</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>31533</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>25154</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>38064</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>56,54%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>45,1%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>68,25%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>27334</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>17262</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>34930</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>49,99%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>31,57%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>63,88%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33631</t>
+          <t>26069</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26506</t>
+          <t>20247</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41020</t>
+          <t>31494</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>60964</t>
+          <t>57602</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49002</t>
+          <t>48414</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71314</t>
+          <t>66614</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>64,97%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9368</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5349</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14658</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>16,8%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9,59%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>26,28%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>14730</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7235</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>28677</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>26,94%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13,23%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>52,45%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11428</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>12097</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>26158</t>
+          <t>16580</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16520</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41636</t>
+          <t>23623</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -1285,72 +1285,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2117</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>728</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5018</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>9,0%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2159</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>5224</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1849</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>4882</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>3,95%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>9,55%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>2500</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>784</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>5190</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -1398,74 +1398,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>55770</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>55770</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>55770</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>46758</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>46758</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>46758</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>61067</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>61067</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>61067</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>151</t>
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>115744</t>
+          <t>102528</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>115744</t>
+          <t>102528</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115744</t>
+          <t>102528</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7207</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4149</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12030</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>12034</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7557</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>19197</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8378</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>7231</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13708</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>20412</t>
+          <t>19123</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14302</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28394</t>
+          <t>26022</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55442</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>44532</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70291</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>11,7%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>14,84%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>33906</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>24161</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>46006</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,4%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,04%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56484</t>
+          <t>32120</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45015</t>
+          <t>24551</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71541</t>
+          <t>41120</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>90390</t>
+          <t>87562</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>73775</t>
+          <t>73251</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>110101</t>
+          <t>105001</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>125026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>105597</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>145891</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>26,39%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>22,29%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>30,8%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>78853</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>62328</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>94773</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>17,21%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13,6%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,68%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>130208</t>
+          <t>82272</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109368</t>
+          <t>68390</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>152368</t>
+          <t>97251</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>209061</t>
+          <t>207299</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>181754</t>
+          <t>184462</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>236416</t>
+          <t>233181</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>207929</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>184941</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>228718</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>43,9%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>39,04%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>48,28%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>324</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>220579</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>182112</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>244163</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>48,14%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>39,75%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>53,29%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>227015</t>
+          <t>224630</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>200730</t>
+          <t>206724</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>250668</t>
+          <t>241417</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>447594</t>
+          <t>432558</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>404786</t>
+          <t>404589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>482251</t>
+          <t>460176</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>50,91%</t>
         </is>
       </c>
     </row>
@@ -1967,72 +1967,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>60993</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>47447</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>87691</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>12,88%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>18,51%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>94704</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>67650</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>170230</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>20,67%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>14,76%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>37,15%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>72636</t>
+          <t>62203</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55737</t>
+          <t>50592</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>105430</t>
+          <t>75715</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>167340</t>
+          <t>123196</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>132668</t>
+          <t>105065</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>240888</t>
+          <t>148881</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18108</t>
+          <t>17088</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12651</t>
+          <t>11176</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26694</t>
+          <t>25628</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>17150</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>11735</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28686</t>
+          <t>24853</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>37434</t>
+          <t>34237</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28768</t>
+          <t>25549</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48199</t>
+          <t>44651</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -2193,74 +2193,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>473684</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>473684</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>473684</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>639</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>458183</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>458183</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>458183</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>430291</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>430291</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>430291</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>514047</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>514047</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>514047</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1289</t>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>972231</t>
+          <t>903975</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>972231</t>
+          <t>903975</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>972231</t>
+          <t>903975</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1707</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4309</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2391</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>915</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>5746</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>34544</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>26337</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>45865</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>20,59%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>15,7%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>27,34%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>19351</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>13424</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>26586</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>12,94%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>8,98%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>17,78%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>36035</t>
+          <t>20248</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27107</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46349</t>
+          <t>28203</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>55386</t>
+          <t>54792</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44608</t>
+          <t>44279</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67742</t>
+          <t>67333</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>43476</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>33768</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>54427</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>25,91%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>20,13%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>32,44%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>39136</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>30604</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>48357</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>26,17%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>20,46%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>32,33%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>47846</t>
+          <t>40446</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36700</t>
+          <t>31592</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61199</t>
+          <t>49898</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>86982</t>
+          <t>83922</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>73585</t>
+          <t>71555</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>103055</t>
+          <t>99160</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,21%</t>
         </is>
       </c>
     </row>
@@ -2649,72 +2649,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>62270</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>52488</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74901</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>37,12%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>31,29%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>44,64%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>62978</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>53486</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>73335</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>63160</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>53029</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>72691</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>42,11%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>35,76%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>49,04%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>66488</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>54681</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>78808</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>36,42%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>129466</t>
+          <t>125430</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>114379</t>
+          <t>110514</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>145099</t>
+          <t>141286</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -2762,72 +2762,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>20932</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>13772</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>28816</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>12,48%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>8,21%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>17,18%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>21474</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>14984</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>29720</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>14,36%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>10,02%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>19,87%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>23610</t>
+          <t>19734</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16562</t>
+          <t>13851</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33123</t>
+          <t>26677</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>45084</t>
+          <t>40665</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35140</t>
+          <t>31716</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55622</t>
+          <t>51230</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -2875,72 +2875,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>4846</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2577</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>9166</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>5,46%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>4221</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>1565</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>8463</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>10222</t>
+          <t>8787</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15816</t>
+          <t>14633</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -2988,74 +2988,74 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>167775</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>167775</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>167775</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>149976</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>149976</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>149976</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>182583</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>182583</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>182583</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>467</t>
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>332134</t>
+          <t>317751</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>332134</t>
+          <t>317751</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>332134</t>
+          <t>317751</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>11067</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>7053</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>17625</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>14855</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>9962</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>21940</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13370</t>
+          <t>14734</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>9282</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19949</t>
+          <t>21132</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>28225</t>
+          <t>25801</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20455</t>
+          <t>18357</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36333</t>
+          <t>34345</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>94319</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>79290</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>113187</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>13,53%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>11,37%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>16,23%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>55847</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>45001</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>71429</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>10,78%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>96789</t>
+          <t>55008</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>81121</t>
+          <t>45317</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>114773</t>
+          <t>67697</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>152636</t>
+          <t>149328</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>130717</t>
+          <t>130896</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>173814</t>
+          <t>172229</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -3331,72 +3331,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>174766</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>152743</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>199469</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>25,07%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>21,91%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>28,61%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>125424</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>105792</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>145147</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>18,93%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>15,97%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>21,91%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>184903</t>
+          <t>131338</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>164197</t>
+          <t>113756</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>211456</t>
+          <t>149282</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>310327</t>
+          <t>306104</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>275879</t>
+          <t>276630</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>340590</t>
+          <t>336407</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>25,4%</t>
         </is>
       </c>
     </row>
@@ -3444,72 +3444,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>301731</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>277875</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>327411</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>43,28%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>39,85%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>46,96%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>455</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>310890</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>270023</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>338815</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>46,93%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>40,76%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>51,15%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>327134</t>
+          <t>313858</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>300735</t>
+          <t>292418</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>354232</t>
+          <t>335749</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>638024</t>
+          <t>615590</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>588080</t>
+          <t>582245</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>676870</t>
+          <t>647534</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>48,9%</t>
         </is>
       </c>
     </row>
@@ -3557,72 +3557,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>91293</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>76625</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>120786</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>13,09%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>10,99%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>17,32%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>130908</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>99267</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>206647</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>19,76%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>14,99%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>31,2%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>107675</t>
+          <t>89148</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>89522</t>
+          <t>75384</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>140398</t>
+          <t>104573</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>238583</t>
+          <t>180441</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>200870</t>
+          <t>159243</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>318556</t>
+          <t>208416</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -3670,72 +3670,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>24051</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>17939</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>33343</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>24488</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>17978</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>33905</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>27826</t>
+          <t>22939</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>20456</t>
+          <t>16573</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>37459</t>
+          <t>32396</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>52314</t>
+          <t>46990</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>41479</t>
+          <t>37567</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>65192</t>
+          <t>59864</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -3783,74 +3783,74 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>938</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>662412</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>662412</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>662412</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>627025</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>627025</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>627025</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>757697</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>757697</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>757697</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>1907</t>
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1420109</t>
+          <t>1324254</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1420109</t>
+          <t>1324254</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1420109</t>
+          <t>1324254</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">

--- a/data/trans_orig/IP24_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP24_2023-Estudios-trans_orig.xlsx
@@ -1007,7 +1007,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
@@ -1508,7 +1508,7 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -2009,7 +2009,7 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -2510,7 +2510,7 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
